--- a/diseases/d103/2020-2025.xlsx
+++ b/diseases/d103/2020-2025.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3144,6 +3224,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO18" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3292,6 +3377,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO19" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3440,6 +3530,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3588,6 +3683,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3736,6 +3836,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3884,6 +3989,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4032,6 +4142,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4180,6 +4295,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4328,6 +4448,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4476,6 +4601,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4624,6 +4754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4772,6 +4907,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4920,6 +5060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5068,6 +5213,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO31" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5216,6 +5366,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5364,6 +5519,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5512,6 +5672,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5660,6 +5825,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO35" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5808,6 +5978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5956,6 +6131,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6104,6 +6284,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6252,6 +6437,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6400,6 +6590,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6548,6 +6743,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6696,6 +6896,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO42" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6844,6 +7049,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6992,6 +7202,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO44" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7140,6 +7355,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7288,6 +7508,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7436,6 +7661,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7584,6 +7814,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7732,6 +7967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7880,6 +8120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8028,6 +8273,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8176,6 +8426,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8324,6 +8579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8472,6 +8732,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8620,6 +8885,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO55" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8768,6 +9038,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO56" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8916,6 +9191,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9064,6 +9344,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO58" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9212,6 +9497,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO59" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9360,6 +9650,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9508,6 +9803,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9656,6 +9956,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9804,6 +10109,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO63" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9952,6 +10262,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO64" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10100,6 +10415,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO65" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10248,6 +10568,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO66" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10396,6 +10721,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO67" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10544,6 +10874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO68" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10692,6 +11027,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO69" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10840,6 +11180,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO70" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10988,6 +11333,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11136,6 +11486,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11284,6 +11639,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11432,6 +11792,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO74" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11580,6 +11945,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO75" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11728,6 +12098,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11876,6 +12251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO77" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12024,6 +12404,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO78" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12172,6 +12557,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO79" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12320,6 +12710,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO80" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12468,6 +12863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO81" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12616,6 +13016,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12764,6 +13169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -12912,6 +13322,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13060,6 +13475,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO85" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13208,6 +13628,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13356,6 +13781,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO87" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13504,6 +13934,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13652,6 +14087,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13800,6 +14240,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13948,6 +14393,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14096,6 +14546,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14244,6 +14699,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14392,6 +14852,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14540,6 +15005,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14688,6 +15158,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14836,6 +15311,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14984,6 +15464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO98" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15132,6 +15617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO99" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15280,6 +15770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15428,6 +15923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO101" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15576,6 +16076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO102" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15724,6 +16229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15872,6 +16382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO104" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16020,6 +16535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO105" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16168,6 +16688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO106" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16316,6 +16841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO107" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16464,6 +16994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO108" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16612,6 +17147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO109" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16760,6 +17300,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO110" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16908,6 +17453,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO111" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17056,6 +17606,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO112" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17204,6 +17759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO113" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17352,6 +17912,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO114" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17500,6 +18065,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO115" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17648,6 +18218,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO116" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17796,6 +18371,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17944,6 +18524,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO118" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18092,6 +18677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO119" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18240,6 +18830,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO120" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18388,6 +18983,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO121" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18536,6 +19136,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO122" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18684,6 +19289,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18832,6 +19442,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO124" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -18980,6 +19595,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19128,6 +19748,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO126" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19276,6 +19901,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19424,6 +20054,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO128" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19572,6 +20207,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19720,6 +20360,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19868,6 +20513,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20016,6 +20666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20164,6 +20819,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20312,6 +20972,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20460,6 +21125,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20608,6 +21278,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20756,6 +21431,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20904,6 +21584,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21052,6 +21737,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO139" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21200,6 +21890,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO140" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21348,6 +22043,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21496,6 +22196,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO142" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21644,6 +22349,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO143" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21792,6 +22502,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO144" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21940,6 +22655,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO145" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22088,6 +22808,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO146" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22236,6 +22961,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO147" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22384,6 +23114,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO148" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22532,6 +23267,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO149" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22680,6 +23420,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO150" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22828,6 +23573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO151" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22976,6 +23726,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO152" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23124,6 +23879,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO153" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23272,6 +24032,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO154" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23420,6 +24185,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO155" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23568,6 +24338,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO156" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23716,6 +24491,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO157" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23864,6 +24644,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24012,6 +24797,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO159" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24160,6 +24950,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO160" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24308,6 +25103,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO161" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24456,6 +25256,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO162" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24604,6 +25409,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO163" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24752,6 +25562,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24900,6 +25715,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO165" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25048,6 +25868,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25196,6 +26021,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO167" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25344,6 +26174,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25492,6 +26327,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO169" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25640,6 +26480,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25788,6 +26633,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -25936,6 +26786,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26084,6 +26939,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26232,6 +27092,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26380,6 +27245,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26528,6 +27398,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26676,6 +27551,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26824,6 +27704,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -26972,6 +27857,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27120,6 +28010,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO180" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27268,6 +28163,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO181" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27416,6 +28316,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27564,6 +28469,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO183" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27712,6 +28622,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO184" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27860,6 +28775,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO185" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28008,6 +28928,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO186" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28156,6 +29081,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO187" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28304,6 +29234,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA188" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO188" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28452,6 +29387,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA189" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO189" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28600,6 +29540,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA190" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO190" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28748,6 +29693,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA191" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO191" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28896,6 +29846,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA192" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO192" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29044,6 +29999,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA193" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO193" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29192,6 +30152,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA194" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO194" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29340,6 +30305,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA195" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO195" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29488,6 +30458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA196" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO196" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29636,6 +30611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA197" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO197" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29784,6 +30764,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA198" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO198" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29932,6 +30917,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA199" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO199" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30080,6 +31070,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA200" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO200" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30228,6 +31223,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30376,6 +31376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA202" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO202" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30524,6 +31529,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA203" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO203" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30672,6 +31682,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA204" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO204" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30820,6 +31835,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA205" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO205" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30968,6 +31988,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA206" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO206" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31116,6 +32141,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31264,6 +32294,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA208" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO208" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31412,6 +32447,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31560,6 +32600,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA210" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO210" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31708,6 +32753,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31856,6 +32906,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA212" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO212" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32004,6 +33059,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32152,6 +33212,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA214" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO214" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32300,6 +33365,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32448,6 +33518,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32596,6 +33671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32744,6 +33824,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -32892,6 +33977,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33040,6 +34130,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33188,6 +34283,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33336,6 +34436,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33484,6 +34589,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33632,6 +34742,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33780,6 +34895,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO225" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -33928,6 +35048,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA226" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34076,6 +35201,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34224,6 +35354,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA228" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO228" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34372,6 +35507,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA229" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO229" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34520,6 +35660,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA230" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO230" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34668,6 +35813,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA231" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO231" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34816,6 +35966,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO232" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -34964,6 +36119,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO233" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35112,6 +36272,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO234" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35260,6 +36425,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO235" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35408,6 +36578,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO236" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35556,6 +36731,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO237" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35704,6 +36884,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO238" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35852,6 +37037,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO239" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36000,6 +37190,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO240" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36148,6 +37343,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO241" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36296,6 +37496,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO242" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36444,6 +37649,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36592,6 +37802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36740,6 +37955,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36888,6 +38108,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO246" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37036,6 +38261,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37184,6 +38414,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO248" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37332,6 +38567,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37480,6 +38720,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37628,6 +38873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO251" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37776,6 +39026,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37924,6 +39179,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO253" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38072,6 +39332,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38220,6 +39485,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO255" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38368,6 +39638,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38516,6 +39791,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38664,6 +39944,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38812,6 +40097,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38960,6 +40250,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39108,6 +40403,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39256,6 +40556,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39404,6 +40709,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39552,6 +40862,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39700,6 +41015,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39848,6 +41168,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO266" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39996,6 +41321,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO267" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40144,6 +41474,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40292,6 +41627,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO269" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40440,6 +41780,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40588,6 +41933,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40736,6 +42086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -40884,6 +42239,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO273" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41032,6 +42392,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO274" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41180,6 +42545,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO275" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41328,6 +42698,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO276" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41476,6 +42851,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO277" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41624,6 +43004,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO278" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41772,6 +43157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO279" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -41920,6 +43310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO280" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42068,6 +43463,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO281" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42216,6 +43616,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO282" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42362,6 +43767,11 @@
       <c r="S283" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO283" t="inlineStr">

--- a/diseases/d103/2020-2025.xlsx
+++ b/diseases/d103/2020-2025.xlsx
@@ -12699,9 +12699,6 @@
       <c r="O80" t="n">
         <v>1</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -12852,9 +12849,6 @@
       <c r="O81" t="n">
         <v>1</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -13005,9 +12999,6 @@
       <c r="O82" t="n">
         <v>1</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -13923,9 +13914,6 @@
       <c r="O88" t="n">
         <v>2</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -14229,9 +14217,6 @@
       <c r="O90" t="n">
         <v>2</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -14382,9 +14367,6 @@
       <c r="O91" t="n">
         <v>1</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -14688,9 +14670,6 @@
       <c r="O93" t="n">
         <v>2</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -14841,9 +14820,6 @@
       <c r="O94" t="n">
         <v>2</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -14994,9 +14970,6 @@
       <c r="O95" t="n">
         <v>1</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -15300,9 +15273,6 @@
       <c r="O97" t="n">
         <v>2</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -15453,9 +15423,6 @@
       <c r="O98" t="n">
         <v>1</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -15606,9 +15573,6 @@
       <c r="O99" t="n">
         <v>2</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -15759,9 +15723,6 @@
       <c r="O100" t="n">
         <v>2</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -15912,9 +15873,6 @@
       <c r="O101" t="n">
         <v>5</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -16065,9 +16023,6 @@
       <c r="O102" t="n">
         <v>1</v>
       </c>
-      <c r="Q102" t="n">
-        <v>0</v>
-      </c>
       <c r="R102" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16218,9 +16173,6 @@
       <c r="O103" t="n">
         <v>2</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16371,9 +16323,6 @@
       <c r="O104" t="n">
         <v>2</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -16524,9 +16473,6 @@
       <c r="O105" t="n">
         <v>3</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -16677,9 +16623,6 @@
       <c r="O106" t="n">
         <v>3</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -16830,9 +16773,6 @@
       <c r="O107" t="n">
         <v>1</v>
       </c>
-      <c r="Q107" t="n">
-        <v>0</v>
-      </c>
       <c r="R107" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -16983,9 +16923,6 @@
       <c r="O108" t="n">
         <v>1</v>
       </c>
-      <c r="Q108" t="n">
-        <v>0</v>
-      </c>
       <c r="R108" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -17136,9 +17073,6 @@
       <c r="O109" t="n">
         <v>1</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -17289,9 +17223,6 @@
       <c r="O110" t="n">
         <v>3</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.0008783897358191777</v>
       </c>
@@ -17442,9 +17373,6 @@
       <c r="O111" t="n">
         <v>2</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -17595,9 +17523,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -17748,9 +17673,6 @@
       <c r="O113" t="n">
         <v>1</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -17901,9 +17823,6 @@
       <c r="O114" t="n">
         <v>5</v>
       </c>
-      <c r="Q114" t="n">
-        <v>0</v>
-      </c>
       <c r="R114" t="n">
         <v>0.001463982893031963</v>
       </c>
@@ -18054,9 +17973,6 @@
       <c r="O115" t="n">
         <v>1</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -18207,9 +18123,6 @@
       <c r="O116" t="n">
         <v>2</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -18513,9 +18426,6 @@
       <c r="O118" t="n">
         <v>1</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -18666,9 +18576,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -18819,9 +18726,6 @@
       <c r="O120" t="n">
         <v>1</v>
       </c>
-      <c r="Q120" t="n">
-        <v>0</v>
-      </c>
       <c r="R120" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -18972,9 +18876,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -19278,9 +19179,6 @@
       <c r="O123" t="n">
         <v>2</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.000585593157212785</v>
       </c>
@@ -19431,9 +19329,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.0002927965786063925</v>
       </c>
@@ -20043,9 +19938,6 @@
       <c r="O128" t="n">
         <v>1</v>
       </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
       <c r="R128" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -20196,9 +20088,6 @@
       <c r="O129" t="n">
         <v>5</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.001455700126472683</v>
       </c>
@@ -20349,9 +20238,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -20502,9 +20388,6 @@
       <c r="O131" t="n">
         <v>1</v>
       </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
       <c r="R131" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -20655,9 +20538,6 @@
       <c r="O132" t="n">
         <v>1</v>
       </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
       <c r="R132" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -20808,9 +20688,6 @@
       <c r="O133" t="n">
         <v>2</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -20961,9 +20838,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -21267,9 +21141,6 @@
       <c r="O136" t="n">
         <v>1</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -21420,9 +21291,6 @@
       <c r="O137" t="n">
         <v>2</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -21573,9 +21441,6 @@
       <c r="O138" t="n">
         <v>1</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -21726,9 +21591,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -21879,9 +21741,6 @@
       <c r="O140" t="n">
         <v>1</v>
       </c>
-      <c r="Q140" t="n">
-        <v>0</v>
-      </c>
       <c r="R140" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -22491,9 +22350,6 @@
       <c r="O144" t="n">
         <v>1</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -22797,9 +22653,6 @@
       <c r="O146" t="n">
         <v>3</v>
       </c>
-      <c r="Q146" t="n">
-        <v>0</v>
-      </c>
       <c r="R146" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -22950,9 +22803,6 @@
       <c r="O147" t="n">
         <v>3</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -23256,9 +23106,6 @@
       <c r="O149" t="n">
         <v>3</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -23409,9 +23256,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -23562,9 +23406,6 @@
       <c r="O151" t="n">
         <v>1</v>
       </c>
-      <c r="Q151" t="n">
-        <v>0</v>
-      </c>
       <c r="R151" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -23715,9 +23556,6 @@
       <c r="O152" t="n">
         <v>1</v>
       </c>
-      <c r="Q152" t="n">
-        <v>0</v>
-      </c>
       <c r="R152" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -23868,9 +23706,6 @@
       <c r="O153" t="n">
         <v>1</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24021,9 +23856,6 @@
       <c r="O154" t="n">
         <v>2</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -24174,9 +24006,6 @@
       <c r="O155" t="n">
         <v>3</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -24327,9 +24156,6 @@
       <c r="O156" t="n">
         <v>2</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -24480,9 +24306,6 @@
       <c r="O157" t="n">
         <v>1</v>
       </c>
-      <c r="Q157" t="n">
-        <v>0</v>
-      </c>
       <c r="R157" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24633,9 +24456,6 @@
       <c r="O158" t="n">
         <v>2</v>
       </c>
-      <c r="Q158" t="n">
-        <v>0</v>
-      </c>
       <c r="R158" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -24786,9 +24606,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -24939,9 +24756,6 @@
       <c r="O160" t="n">
         <v>3</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -25092,9 +24906,6 @@
       <c r="O161" t="n">
         <v>3</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -25245,9 +25056,6 @@
       <c r="O162" t="n">
         <v>2</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -25398,9 +25206,6 @@
       <c r="O163" t="n">
         <v>4</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -25551,9 +25356,6 @@
       <c r="O164" t="n">
         <v>1</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -25704,9 +25506,6 @@
       <c r="O165" t="n">
         <v>2</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -25857,9 +25656,6 @@
       <c r="O166" t="n">
         <v>2</v>
       </c>
-      <c r="Q166" t="n">
-        <v>0</v>
-      </c>
       <c r="R166" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -26010,9 +25806,6 @@
       <c r="O167" t="n">
         <v>4</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.001164560101178146</v>
       </c>
@@ -26163,9 +25956,6 @@
       <c r="O168" t="n">
         <v>3</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -26316,9 +26106,6 @@
       <c r="O169" t="n">
         <v>2</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -26469,9 +26256,6 @@
       <c r="O170" t="n">
         <v>3</v>
       </c>
-      <c r="Q170" t="n">
-        <v>0</v>
-      </c>
       <c r="R170" t="n">
         <v>0.0008734200758836097</v>
       </c>
@@ -26622,9 +26406,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -26775,9 +26556,6 @@
       <c r="O172" t="n">
         <v>1</v>
       </c>
-      <c r="Q172" t="n">
-        <v>0</v>
-      </c>
       <c r="R172" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -26928,9 +26706,6 @@
       <c r="O173" t="n">
         <v>1</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -27081,9 +26856,6 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.0002911400252945365</v>
       </c>
@@ -27387,9 +27159,6 @@
       <c r="O176" t="n">
         <v>2</v>
       </c>
-      <c r="Q176" t="n">
-        <v>0</v>
-      </c>
       <c r="R176" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -27693,9 +27462,6 @@
       <c r="O178" t="n">
         <v>2</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.0005822800505890731</v>
       </c>
@@ -27999,9 +27765,6 @@
       <c r="O180" t="n">
         <v>1</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -28305,9 +28068,6 @@
       <c r="O182" t="n">
         <v>1</v>
       </c>
-      <c r="Q182" t="n">
-        <v>0</v>
-      </c>
       <c r="R182" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -28764,9 +28524,6 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -29223,9 +28980,6 @@
       <c r="O188" t="n">
         <v>1</v>
       </c>
-      <c r="Q188" t="n">
-        <v>0</v>
-      </c>
       <c r="R188" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -29376,9 +29130,6 @@
       <c r="O189" t="n">
         <v>1</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -29529,9 +29280,6 @@
       <c r="O190" t="n">
         <v>1</v>
       </c>
-      <c r="Q190" t="n">
-        <v>0</v>
-      </c>
       <c r="R190" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -29988,9 +29736,6 @@
       <c r="O193" t="n">
         <v>1</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -30141,9 +29886,6 @@
       <c r="O194" t="n">
         <v>2</v>
       </c>
-      <c r="Q194" t="n">
-        <v>0</v>
-      </c>
       <c r="R194" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -30294,9 +30036,6 @@
       <c r="O195" t="n">
         <v>2</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -30447,9 +30186,6 @@
       <c r="O196" t="n">
         <v>1</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -30600,9 +30336,6 @@
       <c r="O197" t="n">
         <v>5</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0.001447485636534892</v>
       </c>
@@ -30753,9 +30486,6 @@
       <c r="O198" t="n">
         <v>1</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -31212,9 +30942,6 @@
       <c r="O201" t="n">
         <v>2</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31365,9 +31092,6 @@
       <c r="O202" t="n">
         <v>3</v>
       </c>
-      <c r="Q202" t="n">
-        <v>0</v>
-      </c>
       <c r="R202" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -31518,9 +31242,6 @@
       <c r="O203" t="n">
         <v>7</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0.002026479891148849</v>
       </c>
@@ -31671,9 +31392,6 @@
       <c r="O204" t="n">
         <v>3</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -31824,9 +31542,6 @@
       <c r="O205" t="n">
         <v>2</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -31977,9 +31692,6 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32130,9 +31842,6 @@
       <c r="O207" t="n">
         <v>1</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32436,9 +32145,6 @@
       <c r="O209" t="n">
         <v>1</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -32589,9 +32295,6 @@
       <c r="O210" t="n">
         <v>3</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -32742,9 +32445,6 @@
       <c r="O211" t="n">
         <v>3</v>
       </c>
-      <c r="Q211" t="n">
-        <v>0</v>
-      </c>
       <c r="R211" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -33048,9 +32748,6 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -33201,9 +32898,6 @@
       <c r="O214" t="n">
         <v>4</v>
       </c>
-      <c r="Q214" t="n">
-        <v>0</v>
-      </c>
       <c r="R214" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -33354,9 +33048,6 @@
       <c r="O215" t="n">
         <v>1</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -33660,9 +33351,6 @@
       <c r="O217" t="n">
         <v>3</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -33813,9 +33501,6 @@
       <c r="O218" t="n">
         <v>4</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -33966,9 +33651,6 @@
       <c r="O219" t="n">
         <v>2</v>
       </c>
-      <c r="Q219" t="n">
-        <v>0</v>
-      </c>
       <c r="R219" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -34272,9 +33954,6 @@
       <c r="O221" t="n">
         <v>2</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -34425,9 +34104,6 @@
       <c r="O222" t="n">
         <v>3</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -34578,9 +34254,6 @@
       <c r="O223" t="n">
         <v>1</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -34731,9 +34404,6 @@
       <c r="O224" t="n">
         <v>2</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.0005789942546139568</v>
       </c>
@@ -34884,9 +34554,6 @@
       <c r="O225" t="n">
         <v>3</v>
       </c>
-      <c r="Q225" t="n">
-        <v>0</v>
-      </c>
       <c r="R225" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -35037,9 +34704,6 @@
       <c r="O226" t="n">
         <v>4</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0.001157988509227914</v>
       </c>
@@ -35190,9 +34854,6 @@
       <c r="O227" t="n">
         <v>3</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0.0008684913819209351</v>
       </c>
@@ -35343,9 +35004,6 @@
       <c r="O228" t="n">
         <v>1</v>
       </c>
-      <c r="Q228" t="n">
-        <v>0</v>
-      </c>
       <c r="R228" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -35649,9 +35307,6 @@
       <c r="O230" t="n">
         <v>1</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -35802,9 +35457,6 @@
       <c r="O231" t="n">
         <v>1</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.0002894971273069784</v>
       </c>
@@ -35955,9 +35607,6 @@
       <c r="O232" t="n">
         <v>2</v>
       </c>
-      <c r="Q232" t="n">
-        <v>0</v>
-      </c>
       <c r="R232" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -36108,9 +35757,6 @@
       <c r="O233" t="n">
         <v>3</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -36261,9 +35907,6 @@
       <c r="O234" t="n">
         <v>2</v>
       </c>
-      <c r="Q234" t="n">
-        <v>0</v>
-      </c>
       <c r="R234" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -36567,9 +36210,6 @@
       <c r="O236" t="n">
         <v>2</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -36720,9 +36360,6 @@
       <c r="O237" t="n">
         <v>1</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -36873,9 +36510,6 @@
       <c r="O238" t="n">
         <v>2</v>
       </c>
-      <c r="Q238" t="n">
-        <v>0</v>
-      </c>
       <c r="R238" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -37026,9 +36660,6 @@
       <c r="O239" t="n">
         <v>2</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -37179,9 +36810,6 @@
       <c r="O240" t="n">
         <v>2</v>
       </c>
-      <c r="Q240" t="n">
-        <v>0</v>
-      </c>
       <c r="R240" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -37332,9 +36960,6 @@
       <c r="O241" t="n">
         <v>3</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -37944,9 +37569,6 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -38097,9 +37719,6 @@
       <c r="O246" t="n">
         <v>4</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0.001151822244341049</v>
       </c>
@@ -38250,9 +37869,6 @@
       <c r="O247" t="n">
         <v>1</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -38403,9 +38019,6 @@
       <c r="O248" t="n">
         <v>1</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -38556,9 +38169,6 @@
       <c r="O249" t="n">
         <v>3</v>
       </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
       <c r="R249" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -38709,9 +38319,6 @@
       <c r="O250" t="n">
         <v>2</v>
       </c>
-      <c r="Q250" t="n">
-        <v>0</v>
-      </c>
       <c r="R250" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -38862,9 +38469,6 @@
       <c r="O251" t="n">
         <v>3</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -39015,9 +38619,6 @@
       <c r="O252" t="n">
         <v>1</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -39168,9 +38769,6 @@
       <c r="O253" t="n">
         <v>2</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -39321,9 +38919,6 @@
       <c r="O254" t="n">
         <v>3</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -39474,9 +39069,6 @@
       <c r="O255" t="n">
         <v>3</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -39627,9 +39219,6 @@
       <c r="O256" t="n">
         <v>2</v>
       </c>
-      <c r="Q256" t="n">
-        <v>0</v>
-      </c>
       <c r="R256" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -39933,9 +39522,6 @@
       <c r="O258" t="n">
         <v>2</v>
       </c>
-      <c r="Q258" t="n">
-        <v>0</v>
-      </c>
       <c r="R258" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -40086,9 +39672,6 @@
       <c r="O259" t="n">
         <v>1</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -40239,9 +39822,6 @@
       <c r="O260" t="n">
         <v>1</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -40392,9 +39972,6 @@
       <c r="O261" t="n">
         <v>3</v>
       </c>
-      <c r="Q261" t="n">
-        <v>0</v>
-      </c>
       <c r="R261" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -40545,9 +40122,6 @@
       <c r="O262" t="n">
         <v>3</v>
       </c>
-      <c r="Q262" t="n">
-        <v>0</v>
-      </c>
       <c r="R262" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -40698,9 +40272,6 @@
       <c r="O263" t="n">
         <v>5</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.001439777805426311</v>
       </c>
@@ -40851,9 +40422,6 @@
       <c r="O264" t="n">
         <v>2</v>
       </c>
-      <c r="Q264" t="n">
-        <v>0</v>
-      </c>
       <c r="R264" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -41004,9 +40572,6 @@
       <c r="O265" t="n">
         <v>2</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -41157,9 +40722,6 @@
       <c r="O266" t="n">
         <v>1</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -41310,9 +40872,6 @@
       <c r="O267" t="n">
         <v>2</v>
       </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
       <c r="R267" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -41616,9 +41175,6 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -41769,9 +41325,6 @@
       <c r="O270" t="n">
         <v>2</v>
       </c>
-      <c r="Q270" t="n">
-        <v>0</v>
-      </c>
       <c r="R270" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -41922,9 +41475,6 @@
       <c r="O271" t="n">
         <v>3</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -42228,9 +41778,6 @@
       <c r="O273" t="n">
         <v>1</v>
       </c>
-      <c r="Q273" t="n">
-        <v>0</v>
-      </c>
       <c r="R273" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -42381,9 +41928,6 @@
       <c r="O274" t="n">
         <v>2</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -42534,9 +42078,6 @@
       <c r="O275" t="n">
         <v>1</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -42687,9 +42228,6 @@
       <c r="O276" t="n">
         <v>3</v>
       </c>
-      <c r="Q276" t="n">
-        <v>0</v>
-      </c>
       <c r="R276" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -42840,9 +42378,6 @@
       <c r="O277" t="n">
         <v>1</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0.0002879555610852622</v>
       </c>
@@ -42993,9 +42528,6 @@
       <c r="O278" t="n">
         <v>5</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.001439777805426311</v>
       </c>
@@ -43452,9 +42984,6 @@
       <c r="O281" t="n">
         <v>3</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.0008638666832557865</v>
       </c>
@@ -43605,9 +43134,6 @@
       <c r="O282" t="n">
         <v>2</v>
       </c>
-      <c r="Q282" t="n">
-        <v>0</v>
-      </c>
       <c r="R282" t="n">
         <v>0.0005759111221705244</v>
       </c>
@@ -43757,9 +43283,6 @@
       </c>
       <c r="O283" t="n">
         <v>3</v>
-      </c>
-      <c r="Q283" t="n">
-        <v>0</v>
       </c>
       <c r="R283" t="n">
         <v>0.0008638666832557865</v>
